--- a/data/trans_camb/IP2005-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 5,64</t>
+          <t>-6,78; 5,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 7,75</t>
+          <t>-4,85; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,4; -1,82</t>
+          <t>-17,07; -2,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 11,12</t>
+          <t>-2,64; 10,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 8,36</t>
+          <t>-6,17; 7,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 6,27</t>
+          <t>-7,87; 5,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 6,44</t>
+          <t>-2,35; 6,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,76</t>
+          <t>-3,63; 5,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 0,19</t>
+          <t>-9,78; -0,44</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 6,34</t>
+          <t>-7,04; 6,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 8,45</t>
+          <t>-5,04; 8,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -2,04</t>
+          <t>-18,08; -2,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 12,95</t>
+          <t>-2,76; 12,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 9,54</t>
+          <t>-6,54; 8,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 7,18</t>
+          <t>-8,41; 6,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 7,16</t>
+          <t>-2,44; 7,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,42</t>
+          <t>-3,84; 6,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 0,18</t>
+          <t>-10,47; -0,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 7,23</t>
+          <t>-6,44; 7,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 9,47</t>
+          <t>-2,44; 10,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 0,82</t>
+          <t>-16,19; -0,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 11,91</t>
+          <t>-0,46; 11,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 7,91</t>
+          <t>-4,98; 8,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 3,68</t>
+          <t>-12,14; 3,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 7,54</t>
+          <t>-1,14; 8,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 7,06</t>
+          <t>-1,87; 7,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 0,31</t>
+          <t>-10,54; -0,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 8,38</t>
+          <t>-6,72; 8,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 10,97</t>
+          <t>-2,45; 11,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 1,14</t>
+          <t>-16,88; -0,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 13,88</t>
+          <t>-0,42; 13,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,07</t>
+          <t>-5,17; 10,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 4,17</t>
+          <t>-12,89; 4,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,53</t>
+          <t>-1,21; 9,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,93</t>
+          <t>-2,0; 8,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 0,29</t>
+          <t>-11,17; -0,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 7,76</t>
+          <t>-9,55; 7,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 13,75</t>
+          <t>-3,24; 12,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 9,94</t>
+          <t>-8,95; 9,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 8,34</t>
+          <t>-5,59; 8,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 10,03</t>
+          <t>-2,93; 10,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 5,18</t>
+          <t>-12,45; 6,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,55</t>
+          <t>-6,35; 5,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 9,01</t>
+          <t>-1,13; 9,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 4,9</t>
+          <t>-8,31; 5,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 9,27</t>
+          <t>-10,17; 8,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 16,92</t>
+          <t>-3,53; 15,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 11,54</t>
+          <t>-9,72; 11,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 9,75</t>
+          <t>-5,95; 9,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 11,54</t>
+          <t>-3,11; 11,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 5,8</t>
+          <t>-13,29; 7,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 6,38</t>
+          <t>-6,83; 6,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 10,35</t>
+          <t>-1,2; 10,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 5,56</t>
+          <t>-9,2; 6,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 8,23</t>
+          <t>-2,64; 7,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,55</t>
+          <t>-1,75; 8,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 8,01</t>
+          <t>-3,36; 8,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 10,05</t>
+          <t>0,08; 9,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 5,29</t>
+          <t>-5,54; 4,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 4,13</t>
+          <t>-7,84; 4,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 7,65</t>
+          <t>0,42; 7,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,75</t>
+          <t>-2,08; 5,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 4,19</t>
+          <t>-4,11; 4,07</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 9,93</t>
+          <t>-2,78; 9,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 10,18</t>
+          <t>-1,93; 9,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 9,47</t>
+          <t>-3,79; 9,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 11,86</t>
+          <t>0,12; 11,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 6,29</t>
+          <t>-6,14; 5,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 4,61</t>
+          <t>-8,66; 4,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 8,95</t>
+          <t>0,52; 8,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,7</t>
+          <t>-2,32; 6,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,94</t>
+          <t>-4,58; 4,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 5,42</t>
+          <t>-8,76; 4,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 10,82</t>
+          <t>-1,13; 11,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 5,84</t>
+          <t>-8,7; 6,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 5,05</t>
+          <t>-8,97; 5,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 9,37</t>
+          <t>-4,89; 8,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 9,52</t>
+          <t>-3,3; 9,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,6</t>
+          <t>-6,59; 3,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 7,96</t>
+          <t>-1,01; 7,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,02</t>
+          <t>-3,95; 5,9</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 6,35</t>
+          <t>-9,59; 5,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 12,97</t>
+          <t>-1,21; 13,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 7,06</t>
+          <t>-9,45; 7,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 6,0</t>
+          <t>-9,91; 5,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 11,1</t>
+          <t>-5,3; 10,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 11,42</t>
+          <t>-3,54; 11,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 4,15</t>
+          <t>-7,29; 4,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,38</t>
+          <t>-1,11; 9,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 7,07</t>
+          <t>-4,4; 6,85</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,7</t>
+          <t>-2,6; 8,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 4,72</t>
+          <t>-8,46; 4,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 2,8</t>
+          <t>-11,48; 2,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,96; -1,2</t>
+          <t>-16,32; -0,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,31</t>
+          <t>-6,11; 5,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,88; -0,03</t>
+          <t>-17,02; -0,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 0,94</t>
+          <t>-8,92; 0,92</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,55</t>
+          <t>-5,36; 3,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -0,7</t>
+          <t>-11,68; -0,4</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 9,75</t>
+          <t>-2,68; 9,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 5,06</t>
+          <t>-8,7; 5,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 3,0</t>
+          <t>-12,25; 2,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -1,4</t>
+          <t>-16,91; -0,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 5,71</t>
+          <t>-6,31; 6,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,59; -0,29</t>
+          <t>-17,6; -0,34</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 0,95</t>
+          <t>-9,28; 0,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 3,78</t>
+          <t>-5,52; 3,9</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -0,79</t>
+          <t>-12,08; -0,44</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,99</t>
+          <t>-2,67; 2,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,46</t>
+          <t>0,43; 5,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,7</t>
+          <t>-5,28; 0,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,39</t>
+          <t>-0,64; 4,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,94</t>
+          <t>-1,37; 4,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,42</t>
+          <t>-4,33; 1,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,88</t>
+          <t>-0,73; 3,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,87</t>
+          <t>-0,01; 3,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,11</t>
+          <t>-3,84; 0,32</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,34</t>
+          <t>-2,91; 3,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,17</t>
+          <t>0,48; 6,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,79</t>
+          <t>-5,82; 0,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,98</t>
+          <t>-0,7; 4,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,49</t>
+          <t>-1,5; 4,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 1,6</t>
+          <t>-4,74; 1,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,26</t>
+          <t>-0,78; 3,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,34</t>
+          <t>-0,01; 4,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,12</t>
+          <t>-4,22; 0,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,6</t>
+          <t>-6,36; 5,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 7,32</t>
+          <t>-4,45; 7,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -2,35</t>
+          <t>-17,04; -2,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 10,57</t>
+          <t>-2,4; 10,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 7,69</t>
+          <t>-5,68; 7,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 5,24</t>
+          <t>-8,63; 5,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 6,52</t>
+          <t>-2,28; 6,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 5,47</t>
+          <t>-3,26; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,78; -0,44</t>
+          <t>-10,15; -0,49</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 6,29</t>
+          <t>-6,57; 6,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 8,18</t>
+          <t>-4,68; 8,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -2,57</t>
+          <t>-17,9; -2,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 12,31</t>
+          <t>-2,52; 11,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 8,97</t>
+          <t>-6,13; 8,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 6,06</t>
+          <t>-9,07; 5,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,37</t>
+          <t>-2,42; 7,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 6,08</t>
+          <t>-3,45; 6,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -0,57</t>
+          <t>-10,87; -0,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 7,8</t>
+          <t>-6,2; 7,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 10,22</t>
+          <t>-2,71; 9,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,19; -0,07</t>
+          <t>-14,74; 1,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 11,7</t>
+          <t>0,58; 12,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 8,92</t>
+          <t>-4,28; 9,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 3,77</t>
+          <t>-11,47; 4,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 8,12</t>
+          <t>-1,42; 8,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 7,11</t>
+          <t>-2,32; 7,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -0,15</t>
+          <t>-11,39; -0,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 8,93</t>
+          <t>-6,5; 8,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 11,75</t>
+          <t>-2,85; 11,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,88; -0,08</t>
+          <t>-15,95; 1,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 13,62</t>
+          <t>0,58; 14,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 10,22</t>
+          <t>-4,47; 10,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 4,11</t>
+          <t>-12,26; 5,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 9,31</t>
+          <t>-1,47; 9,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 8,06</t>
+          <t>-2,44; 8,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,17; -0,14</t>
+          <t>-12,32; -0,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 7,2</t>
+          <t>-9,38; 7,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 12,69</t>
+          <t>-3,28; 13,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 9,53</t>
+          <t>-7,97; 10,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 8,15</t>
+          <t>-5,87; 7,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 10,13</t>
+          <t>-2,91; 10,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 6,32</t>
+          <t>-12,8; 5,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 5,33</t>
+          <t>-5,35; 5,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,06</t>
+          <t>-0,83; 9,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 5,43</t>
+          <t>-8,23; 5,37</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 8,53</t>
+          <t>-10,07; 9,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 15,09</t>
+          <t>-3,52; 15,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 11,34</t>
+          <t>-8,39; 12,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 9,31</t>
+          <t>-6,25; 9,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 11,82</t>
+          <t>-3,09; 11,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 7,29</t>
+          <t>-13,85; 6,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 6,07</t>
+          <t>-5,79; 6,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 10,46</t>
+          <t>-0,89; 10,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 6,2</t>
+          <t>-8,97; 6,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 7,91</t>
+          <t>-2,58; 7,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 8,28</t>
+          <t>-1,68; 8,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 8,12</t>
+          <t>-3,51; 7,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 9,67</t>
+          <t>-0,35; 9,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,93</t>
+          <t>-5,4; 5,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 4,2</t>
+          <t>-7,48; 4,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,52</t>
+          <t>0,26; 7,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,78</t>
+          <t>-1,99; 5,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,07</t>
+          <t>-3,74; 4,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 9,53</t>
+          <t>-2,84; 9,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 9,84</t>
+          <t>-1,77; 9,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 9,61</t>
+          <t>-3,96; 8,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 11,51</t>
+          <t>-0,38; 11,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 5,8</t>
+          <t>-5,94; 6,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 4,88</t>
+          <t>-8,31; 5,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 8,94</t>
+          <t>0,28; 8,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,71</t>
+          <t>-2,23; 6,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 4,82</t>
+          <t>-4,16; 5,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 4,82</t>
+          <t>-7,81; 5,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 11,54</t>
+          <t>-2,1; 10,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 6,29</t>
+          <t>-8,43; 6,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 5,02</t>
+          <t>-8,42; 5,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 8,48</t>
+          <t>-4,03; 8,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 9,78</t>
+          <t>-3,72; 10,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 3,67</t>
+          <t>-5,89; 3,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 7,74</t>
+          <t>-1,15; 7,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 5,9</t>
+          <t>-3,52; 5,96</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 5,7</t>
+          <t>-8,54; 6,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 13,68</t>
+          <t>-2,24; 12,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 7,32</t>
+          <t>-9,25; 7,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 5,89</t>
+          <t>-9,38; 6,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 10,14</t>
+          <t>-4,52; 10,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 11,77</t>
+          <t>-3,97; 12,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 4,24</t>
+          <t>-6,47; 3,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 9,06</t>
+          <t>-1,26; 9,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 6,85</t>
+          <t>-3,85; 6,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 8,48</t>
+          <t>-2,48; 8,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,91</t>
+          <t>-8,68; 5,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 2,39</t>
+          <t>-12,58; 2,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,32; -0,57</t>
+          <t>-15,86; -1,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 5,63</t>
+          <t>-5,91; 5,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -0,28</t>
+          <t>-16,61; 0,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 0,92</t>
+          <t>-8,75; 1,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,59</t>
+          <t>-5,2; 3,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -0,4</t>
+          <t>-11,29; -0,32</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 9,46</t>
+          <t>-2,52; 9,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 5,49</t>
+          <t>-9,03; 5,53</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 2,53</t>
+          <t>-12,93; 2,56</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,91; -0,65</t>
+          <t>-16,44; -1,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 6,2</t>
+          <t>-6,06; 6,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -0,34</t>
+          <t>-17,0; 0,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 0,92</t>
+          <t>-9,03; 1,15</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,9</t>
+          <t>-5,36; 4,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -0,44</t>
+          <t>-11,75; -0,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,91</t>
+          <t>-2,46; 3,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,35</t>
+          <t>0,34; 5,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,62</t>
+          <t>-5,22; 0,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,37</t>
+          <t>-1,06; 4,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,17</t>
+          <t>-1,35; 3,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,21</t>
+          <t>-4,69; 1,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,03</t>
+          <t>-1,04; 2,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,88</t>
+          <t>0,1; 3,92</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,32</t>
+          <t>-4,11; 0,23</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,27</t>
+          <t>-2,7; 3,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,03</t>
+          <t>0,36; 6,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,62</t>
+          <t>-5,72; 1,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,95</t>
+          <t>-1,15; 4,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,73</t>
+          <t>-1,46; 4,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,36</t>
+          <t>-5,23; 1,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,42</t>
+          <t>-1,13; 3,23</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,36</t>
+          <t>0,12; 4,41</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,36</t>
+          <t>-4,55; 0,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,94</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-9,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-9,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,97</t>
+          <t>-5,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 5,9</t>
+          <t>-1,82; 11,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 7,21</t>
+          <t>-5,96; 8,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,04; -2,21</t>
+          <t>-8,31; 6,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 10,11</t>
+          <t>-6,4; 5,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 7,78</t>
+          <t>-4,33; 7,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 5,18</t>
+          <t>-16,04; -1,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 6,71</t>
+          <t>-2,35; 6,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,83</t>
+          <t>-3,6; 5,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,49</t>
+          <t>-10,36; -0,12</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-1,78%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-0,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-9,93%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,54%</t>
+          <t>-10,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-5,4%</t>
+          <t>-5,72%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 6,56</t>
+          <t>-1,91; 12,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 8,02</t>
+          <t>-6,37; 9,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,9; -2,53</t>
+          <t>-8,97; 7,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 11,69</t>
+          <t>-6,71; 6,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 8,88</t>
+          <t>-4,6; 8,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 5,89</t>
+          <t>-17,37; -1,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 7,52</t>
+          <t>-2,49; 7,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 6,49</t>
+          <t>-3,75; 6,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,87; -0,64</t>
+          <t>-11,03; -0,25</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,99</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,49</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,51</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,63</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-7,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-5,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 7,34</t>
+          <t>0,41; 11,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 9,7</t>
+          <t>-4,99; 7,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 1,14</t>
+          <t>-11,64; 4,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 12,15</t>
+          <t>-6,83; 7,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 9,38</t>
+          <t>-2,07; 9,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 4,74</t>
+          <t>-15,28; 1,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,27</t>
+          <t>-1,29; 7,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,16</t>
+          <t>-1,8; 7,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; -0,18</t>
+          <t>-10,72; 0,35</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-3,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-7,74%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,17%</t>
+          <t>-7,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-5,97%</t>
+          <t>-5,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 8,41</t>
+          <t>0,41; 13,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 11,23</t>
+          <t>-5,11; 9,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 1,07</t>
+          <t>-12,54; 4,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 14,09</t>
+          <t>-7,05; 8,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 10,91</t>
+          <t>-2,19; 10,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 5,44</t>
+          <t>-16,23; 1,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 9,55</t>
+          <t>-1,39; 8,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 8,13</t>
+          <t>-1,9; 7,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -0,3</t>
+          <t>-11,58; 0,38</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,42</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,17</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>4,92</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,67</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 7,72</t>
+          <t>-5,47; 8,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 13,22</t>
+          <t>-3,03; 10,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 10,77</t>
+          <t>-13,08; 5,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 7,95</t>
+          <t>-10,16; 7,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 10,05</t>
+          <t>-1,93; 13,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 5,66</t>
+          <t>-6,37; 10,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 5,61</t>
+          <t>-5,26; 5,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 9,01</t>
+          <t>-0,95; 9,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 5,37</t>
+          <t>-7,38; 5,34</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-2,4%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,59%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5,51%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,95%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-1,08%</t>
+          <t>-0,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 9,07</t>
+          <t>-5,8; 9,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 15,9</t>
+          <t>-3,16; 11,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 12,65</t>
+          <t>-14,47; 6,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 9,14</t>
+          <t>-10,79; 9,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 11,74</t>
+          <t>-2,06; 16,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 6,42</t>
+          <t>-6,7; 12,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 6,49</t>
+          <t>-5,78; 6,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 10,35</t>
+          <t>-0,93; 10,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 6,08</t>
+          <t>-8,07; 5,99</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,04</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,54</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,88</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,09</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,85</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>-1,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 7,76</t>
+          <t>0,18; 10,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 8,01</t>
+          <t>-5,42; 5,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,53</t>
+          <t>-8,48; 3,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 9,71</t>
+          <t>-2,42; 8,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 5,86</t>
+          <t>-1,5; 8,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 4,28</t>
+          <t>-5,97; 5,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 7,37</t>
+          <t>0,51; 7,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,39</t>
+          <t>-1,73; 5,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,69</t>
+          <t>-5,49; 2,6</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-2,32%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>3,05%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,71%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-1,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 9,18</t>
+          <t>0,22; 11,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 9,61</t>
+          <t>-5,91; 6,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 8,9</t>
+          <t>-9,61; 4,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 11,5</t>
+          <t>-2,66; 9,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 6,8</t>
+          <t>-1,57; 10,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 5,06</t>
+          <t>-6,7; 6,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 8,59</t>
+          <t>0,56; 8,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 6,24</t>
+          <t>-1,96; 6,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,49</t>
+          <t>-6,09; 3,03</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>4,39</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 5,84</t>
+          <t>-9,0; 5,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 10,26</t>
+          <t>-4,04; 9,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 6,17</t>
+          <t>-3,61; 9,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 5,37</t>
+          <t>-7,69; 5,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 8,54</t>
+          <t>-1,53; 10,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 10,02</t>
+          <t>-8,64; 5,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,45</t>
+          <t>-6,63; 3,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 7,66</t>
+          <t>-0,6; 7,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,96</t>
+          <t>-3,96; 5,91</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-1,83%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-1,73%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-1,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-1,83%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>-1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 6,82</t>
+          <t>-9,75; 6,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 12,03</t>
+          <t>-4,4; 11,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 7,23</t>
+          <t>-3,91; 11,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 6,42</t>
+          <t>-8,39; 6,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 10,3</t>
+          <t>-1,64; 12,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 12,17</t>
+          <t>-9,31; 6,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,95</t>
+          <t>-7,37; 4,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 9,11</t>
+          <t>-0,65; 9,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 6,95</t>
+          <t>-4,36; 6,89</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-8,35</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-6,52</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,68</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-1,44</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-3,87</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-8,35</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-7,35</t>
+          <t>-3,73</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,6</t>
+          <t>-5,08</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 8,24</t>
+          <t>-15,96; -1,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 5,01</t>
+          <t>-6,32; 5,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 2,39</t>
+          <t>-15,5; 0,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -1,57</t>
+          <t>-2,25; 8,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 5,74</t>
+          <t>-8,28; 4,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 0,17</t>
+          <t>-12,35; 2,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,08</t>
+          <t>-8,6; 0,94</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 3,78</t>
+          <t>-5,46; 3,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,32</t>
+          <t>-10,87; -0,19</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-8,71%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-6,8%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>2,83%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-1,52%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-4,09%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-8,71%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-7,67%</t>
+          <t>-3,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-5,88%</t>
+          <t>-5,33%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 9,05</t>
+          <t>-16,37; -1,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 5,53</t>
+          <t>-6,48; 5,71</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 2,56</t>
+          <t>-15,89; 0,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,44; -1,71</t>
+          <t>-2,29; 9,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,26</t>
+          <t>-8,67; 5,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 0,11</t>
+          <t>-12,75; 3,0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 1,15</t>
+          <t>-8,92; 0,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,05</t>
+          <t>-5,65; 3,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -0,35</t>
+          <t>-11,39; -0,22</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,78</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2,92</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-2,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,25</t>
+          <t>-1,17; 4,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,61</t>
+          <t>-1,53; 3,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 0,89</t>
+          <t>-4,5; 1,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,4</t>
+          <t>-2,6; 2,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,91</t>
+          <t>0,53; 5,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,29</t>
+          <t>-6,18; 0,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,87</t>
+          <t>-1,05; 2,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,92</t>
+          <t>0,28; 3,87</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,23</t>
+          <t>-4,34; -0,24</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-1,7%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>3,23%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-2,62%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1,66%</t>
+          <t>-3,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,12%</t>
+          <t>-2,48%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,68</t>
+          <t>-1,25; 4,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,29</t>
+          <t>-1,65; 4,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 1,01</t>
+          <t>-4,94; 1,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,93</t>
+          <t>-2,83; 3,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,43</t>
+          <t>0,58; 6,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 1,41</t>
+          <t>-6,79; -0,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,23</t>
+          <t>-1,15; 3,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,41</t>
+          <t>0,31; 4,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,23</t>
+          <t>-4,81; -0,27</t>
         </is>
       </c>
     </row>
